--- a/02_DIA_inicio_2026_analisis_assets/rbd_25173_esc-basica-municipal-risopatron_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_25173_esc-basica-municipal-risopatron_nt2_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE91CA5E-482E-466E-A4A5-E8DF2DC37016}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F46F00F3-E699-41AD-96DF-04C531B9C495}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{250F4058-4190-45AA-B362-BD5937969A25}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCED8E7D-8776-4C85-B8D2-83B5C0E71731}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF47BCB2-5571-49AF-9668-7B2B9027A379}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8762D9F2-4D3D-4AE2-A37F-0771ACBF62B3}"/>
 </file>